--- a/output/tncn_review_2026-05-16.xlsx
+++ b/output/tncn_review_2026-05-16.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Luật 109/2025/QH15  |  File: Form bảng thu nhập học Claude code.xlsx  |  Ngày tạo: 16/05/2026 12:33</t>
+          <t>Luật 109/2025/QH15  |  File: output/bang_luong_from_sheets.xlsx  |  Ngày tạo: 16/05/2026 12:53</t>
         </is>
       </c>
     </row>

--- a/output/tncn_review_2026-05-16.xlsx
+++ b/output/tncn_review_2026-05-16.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Luật 109/2025/QH15  |  File: output/bang_luong_from_sheets.xlsx  |  Ngày tạo: 16/05/2026 12:53</t>
+          <t>Luật 109/2025/QH15  |  File: output/bang_luong_from_sheets.xlsx  |  Ngày tạo: 16/05/2026 13:05</t>
         </is>
       </c>
     </row>
